--- a/meeple_back/src/main/resources/game-element/neurons-valley.xlsx
+++ b/meeple_back/src/main/resources/game-element/neurons-valley.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10119"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/biggie/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BF3CDD9-8FC1-0C43-90ED-88DB0C9DFF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30080" yWindow="0" windowWidth="30080" windowHeight="33840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15530" windowHeight="9950" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Chart1" sheetId="2" r:id="rId1"/>
@@ -9401,19 +9400,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -9421,7 +9420,7 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -9429,7 +9428,7 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -9842,9 +9841,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -9854,9 +9850,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9874,7 +9873,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10817,7 +10816,7 @@
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11119,9 +11118,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="2" width="9" style="12"/>
@@ -11140,7 +11139,7 @@
     <col min="18" max="18" width="9" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="22" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" s="22" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>1</v>
       </c>
@@ -11179,11 +11178,11 @@
         <v>58</v>
       </c>
       <c r="N1" s="19"/>
-      <c r="O1" s="40" t="s">
+      <c r="O1" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
       <c r="R1" s="32"/>
       <c r="S1" s="19"/>
       <c r="T1" s="19"/>
@@ -11200,7 +11199,7 @@
       <c r="AE1" s="19"/>
       <c r="AF1" s="19"/>
     </row>
-    <row r="2" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32">
       <c r="A2" s="6">
         <v>0</v>
       </c>
@@ -11250,7 +11249,7 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="1:32" ht="72" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" ht="69">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -11314,7 +11313,7 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:32" ht="84" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" ht="80.5">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -11364,7 +11363,7 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:32" ht="84" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" ht="80.5">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -11428,7 +11427,7 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:32" ht="72" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" ht="69">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -11492,7 +11491,7 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
     </row>
-    <row r="7" spans="1:32" ht="96" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" ht="92">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -11556,7 +11555,7 @@
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
     </row>
-    <row r="8" spans="1:32" ht="84" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" ht="80.5">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -11620,7 +11619,7 @@
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
     </row>
-    <row r="9" spans="1:32" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" ht="46">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -11670,7 +11669,7 @@
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
     </row>
-    <row r="10" spans="1:32" ht="84" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" ht="80.5">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -11734,7 +11733,7 @@
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
     </row>
-    <row r="11" spans="1:32" ht="84" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" ht="80.5">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -11798,7 +11797,7 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
     </row>
-    <row r="12" spans="1:32" ht="120" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" ht="115">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -11848,7 +11847,7 @@
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
     </row>
-    <row r="13" spans="1:32" ht="72" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" ht="69">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -11912,7 +11911,7 @@
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
     </row>
-    <row r="14" spans="1:32" ht="72" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" ht="69">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -11976,7 +11975,7 @@
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
     </row>
-    <row r="15" spans="1:32" ht="72" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" ht="69">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -12026,7 +12025,7 @@
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
     </row>
-    <row r="16" spans="1:32" ht="96" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" ht="80.5">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -12090,7 +12089,7 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
     </row>
-    <row r="17" spans="1:32" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" ht="33.75" customHeight="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -12140,7 +12139,7 @@
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
     </row>
-    <row r="18" spans="1:32" ht="96" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" ht="80.5">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -12204,7 +12203,7 @@
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
     </row>
-    <row r="19" spans="1:32" ht="156" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" ht="149.5">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -12259,7 +12258,7 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
     </row>
-    <row r="20" spans="1:32" ht="84" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" ht="80.5">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -12323,7 +12322,7 @@
       <c r="AE20" s="3"/>
       <c r="AF20" s="3"/>
     </row>
-    <row r="21" spans="1:32" ht="72" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" ht="69">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -12387,7 +12386,7 @@
       <c r="AE21" s="3"/>
       <c r="AF21" s="3"/>
     </row>
-    <row r="22" spans="1:32" ht="121" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" ht="115.5" thickBot="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
@@ -12437,7 +12436,7 @@
       <c r="AE22" s="3"/>
       <c r="AF22" s="3"/>
     </row>
-    <row r="23" spans="1:32" ht="85" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" ht="81" thickTop="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -12495,7 +12494,7 @@
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
     </row>
-    <row r="24" spans="1:32" ht="72" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" ht="69">
       <c r="A24" s="6">
         <v>22</v>
       </c>
@@ -12553,7 +12552,7 @@
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
     </row>
-    <row r="25" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32">
       <c r="A25" s="6">
         <v>23</v>
       </c>
@@ -12597,7 +12596,7 @@
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
     </row>
-    <row r="26" spans="1:32" ht="72" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" ht="69">
       <c r="A26" s="6">
         <v>24</v>
       </c>
@@ -12655,7 +12654,7 @@
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
     </row>
-    <row r="27" spans="1:32" ht="96" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" ht="92">
       <c r="A27" s="6">
         <v>25</v>
       </c>
@@ -12713,7 +12712,7 @@
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
     </row>
-    <row r="28" spans="1:32" ht="84" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" ht="80.5">
       <c r="A28" s="6">
         <v>26</v>
       </c>
@@ -12771,7 +12770,7 @@
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
     </row>
-    <row r="29" spans="1:32" ht="96" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" ht="103.5">
       <c r="A29" s="6">
         <v>27</v>
       </c>
@@ -12829,7 +12828,7 @@
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
     </row>
-    <row r="30" spans="1:32" ht="72" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" ht="69">
       <c r="A30" s="6">
         <v>28</v>
       </c>
@@ -12887,7 +12886,7 @@
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
     </row>
-    <row r="31" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32">
       <c r="A31" s="6">
         <v>29</v>
       </c>
@@ -12931,7 +12930,7 @@
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
     </row>
-    <row r="32" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32">
       <c r="A32" s="6">
         <v>30</v>
       </c>
@@ -12975,7 +12974,7 @@
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
     </row>
-    <row r="33" spans="1:13" ht="72" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ht="69">
       <c r="A33" s="6">
         <v>31</v>
       </c>
@@ -13013,7 +13012,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="84" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ht="80.5">
       <c r="A34" s="6">
         <v>32</v>
       </c>
@@ -13051,7 +13050,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13">
       <c r="A35" s="6">
         <v>33</v>
       </c>
@@ -13074,7 +13073,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="84" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ht="69">
       <c r="A36" s="6">
         <v>34</v>
       </c>
@@ -13112,7 +13111,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ht="33.75" customHeight="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
@@ -13135,7 +13134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="84" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="80.5">
       <c r="A38" s="6">
         <v>36</v>
       </c>
@@ -13173,7 +13172,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13">
       <c r="A39" s="6">
         <v>37</v>
       </c>
@@ -13196,7 +13195,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="84" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" ht="69">
       <c r="A40" s="6">
         <v>38</v>
       </c>
@@ -13234,7 +13233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="85" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="81" thickBot="1">
       <c r="A41" s="7">
         <v>39</v>
       </c>
@@ -13272,7 +13271,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13">
       <c r="A42" s="8"/>
       <c r="F42" s="25"/>
     </row>
@@ -13287,450 +13286,451 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299CE8C4-B42B-EA44-98B3-CE69CD3D87B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="120.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="40" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2">
+        <v>47</v>
+      </c>
+      <c r="B2" s="41">
+        <v>1</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>48</v>
+      </c>
+      <c r="B3" s="41">
+        <v>2</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>49</v>
+      </c>
+      <c r="B4" s="41">
+        <v>3</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>50</v>
+      </c>
+      <c r="B5" s="41">
+        <v>4</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>51</v>
+      </c>
+      <c r="B6" s="41">
+        <v>5</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>52</v>
+      </c>
+      <c r="B7" s="41">
+        <v>6</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>53</v>
+      </c>
+      <c r="B8" s="41">
+        <v>7</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>54</v>
+      </c>
+      <c r="B9" s="41">
+        <v>8</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>55</v>
+      </c>
+      <c r="B10" s="41">
+        <v>9</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>56</v>
+      </c>
+      <c r="B11" s="41">
+        <v>10</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>57</v>
+      </c>
+      <c r="B12" s="41">
+        <v>11</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>58</v>
+      </c>
+      <c r="B13" s="41">
+        <v>12</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>59</v>
+      </c>
+      <c r="B14" s="41">
+        <v>13</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>60</v>
+      </c>
+      <c r="B15" s="41">
+        <v>14</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
         <v>61</v>
       </c>
-      <c r="B2" s="42">
-        <v>1</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>138</v>
+      <c r="B16" s="41">
+        <v>15</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="42" t="s">
+        <v>166</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row r="17" spans="1:4">
+      <c r="A17">
         <v>62</v>
       </c>
-      <c r="B3" s="42">
-        <v>2</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>140</v>
+      <c r="B17" s="41">
+        <v>16</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="42" t="s">
+        <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row r="18" spans="1:4">
+      <c r="A18">
         <v>63</v>
       </c>
-      <c r="B4" s="42">
-        <v>3</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>142</v>
+      <c r="B18" s="41">
+        <v>17</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="42" t="s">
+        <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5">
+    <row r="19" spans="1:4">
+      <c r="A19">
         <v>64</v>
       </c>
-      <c r="B5" s="42">
-        <v>4</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>144</v>
+      <c r="B19" s="41">
+        <v>18</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="20" spans="1:4">
+      <c r="A20">
         <v>65</v>
       </c>
-      <c r="B6" s="42">
-        <v>5</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>146</v>
+      <c r="B20" s="41">
+        <v>19</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="D20" s="42" t="s">
+        <v>174</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="21" spans="1:4">
+      <c r="A21">
         <v>66</v>
       </c>
-      <c r="B7" s="42">
-        <v>6</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>148</v>
+      <c r="B21" s="41">
+        <v>20</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="D21" s="42" t="s">
+        <v>176</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="22" spans="1:4">
+      <c r="A22">
         <v>67</v>
       </c>
-      <c r="B8" s="42">
-        <v>7</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>150</v>
+      <c r="B22" s="41">
+        <v>21</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="42" t="s">
+        <v>178</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row r="23" spans="1:4">
+      <c r="A23">
         <v>68</v>
       </c>
-      <c r="B9" s="42">
-        <v>8</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>152</v>
+      <c r="B23" s="41">
+        <v>22</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" s="42" t="s">
+        <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10">
+    <row r="24" spans="1:4">
+      <c r="A24">
         <v>69</v>
       </c>
-      <c r="B10" s="42">
-        <v>9</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>154</v>
+      <c r="B24" s="41">
+        <v>23</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="D24" s="42" t="s">
+        <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11">
+    <row r="25" spans="1:4">
+      <c r="A25">
         <v>70</v>
       </c>
-      <c r="B11" s="42">
-        <v>10</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>156</v>
+      <c r="B25" s="41">
+        <v>24</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" s="42" t="s">
+        <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12">
+    <row r="26" spans="1:4">
+      <c r="A26">
         <v>71</v>
       </c>
-      <c r="B12" s="42">
-        <v>11</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>158</v>
+      <c r="B26" s="41">
+        <v>25</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13">
+    <row r="27" spans="1:4">
+      <c r="A27">
         <v>72</v>
       </c>
-      <c r="B13" s="42">
-        <v>12</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>159</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>160</v>
+      <c r="B27" s="41">
+        <v>26</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>184</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14">
+    <row r="28" spans="1:4">
+      <c r="A28">
         <v>73</v>
       </c>
-      <c r="B14" s="42">
-        <v>13</v>
-      </c>
-      <c r="C14" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>162</v>
+      <c r="B28" s="41">
+        <v>27</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15">
+    <row r="29" spans="1:4">
+      <c r="A29">
         <v>74</v>
       </c>
-      <c r="B15" s="42">
-        <v>14</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>164</v>
+      <c r="B29" s="41">
+        <v>28</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>188</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16">
+    <row r="30" spans="1:4">
+      <c r="A30">
         <v>75</v>
       </c>
-      <c r="B16" s="42">
-        <v>15</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="D16" s="43" t="s">
-        <v>166</v>
+      <c r="B30" s="41">
+        <v>29</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="42" t="s">
+        <v>190</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17">
+    <row r="31" spans="1:4">
+      <c r="A31">
         <v>76</v>
       </c>
-      <c r="B17" s="42">
-        <v>16</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>77</v>
-      </c>
-      <c r="B18" s="42">
-        <v>17</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>169</v>
-      </c>
-      <c r="D18" s="43" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>78</v>
-      </c>
-      <c r="B19" s="42">
-        <v>18</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="D19" s="43" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>79</v>
-      </c>
-      <c r="B20" s="42">
-        <v>19</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>173</v>
-      </c>
-      <c r="D20" s="43" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>80</v>
-      </c>
-      <c r="B21" s="42">
-        <v>20</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="D21" s="43" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>81</v>
-      </c>
-      <c r="B22" s="42">
-        <v>21</v>
-      </c>
-      <c r="C22" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="D22" s="43" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>82</v>
-      </c>
-      <c r="B23" s="42">
-        <v>22</v>
-      </c>
-      <c r="C23" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="D23" s="43" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>83</v>
-      </c>
-      <c r="B24" s="42">
-        <v>23</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="D24" s="43" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>84</v>
-      </c>
-      <c r="B25" s="42">
-        <v>24</v>
-      </c>
-      <c r="C25" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="D25" s="43" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>85</v>
-      </c>
-      <c r="B26" s="42">
-        <v>25</v>
-      </c>
-      <c r="C26" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>86</v>
-      </c>
-      <c r="B27" s="42">
-        <v>26</v>
-      </c>
-      <c r="C27" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>87</v>
-      </c>
-      <c r="B28" s="42">
-        <v>27</v>
-      </c>
-      <c r="C28" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="D28" s="43" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>88</v>
-      </c>
-      <c r="B29" s="42">
-        <v>28</v>
-      </c>
-      <c r="C29" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>89</v>
-      </c>
-      <c r="B30" s="42">
-        <v>29</v>
-      </c>
-      <c r="C30" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" s="43" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>90</v>
-      </c>
-      <c r="B31" s="42">
+      <c r="B31" s="41">
         <v>30</v>
       </c>
-      <c r="C31" s="43" t="s">
+      <c r="C31" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="D31" s="43" t="s">
+      <c r="D31" s="42" t="s">
         <v>192</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>